--- a/model/Output_Budget/1. Baseline/Grid Search/Output Files/100000/Output_0_0.xlsx
+++ b/model/Output_Budget/1. Baseline/Grid Search/Output Files/100000/Output_0_0.xlsx
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10144950.40989403</v>
+        <v>13476767.25690909</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27457249.52289559</v>
+        <v>30789066.36991068</v>
       </c>
     </row>
     <row r="9">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1803024.648971332</v>
+        <v>-1.398707672358336e-10</v>
       </c>
     </row>
     <row r="11">
@@ -7962,7 +7962,7 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>235.7664149699872</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -7971,7 +7971,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>230.0982114216867</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
@@ -8044,16 +8044,16 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>142.1340339220183</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>131.3417120833333</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>142.5962444444444</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>133.9744074143302</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -8120,16 +8120,16 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>134.8846762812383</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>138.9257839476051</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>138.4565384518428</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -8199,19 +8199,19 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>235.7664149699872</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>230.3462332272727</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>230.0982114216867</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>231.2329957552695</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -8278,7 +8278,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>138.5543797798742</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -8287,13 +8287,13 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>142.5962444444444</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>133.9744074143302</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>139.9817740860215</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -8357,10 +8357,10 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>134.8846762812383</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>138.9257839476051</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -8433,7 +8433,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>220.0898510449805</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -8445,10 +8445,10 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>230.0982114216867</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>231.2329957552695</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -8515,7 +8515,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>138.5543797798742</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -8524,13 +8524,13 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>142.5962444444444</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>133.9744074143302</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>139.9817740860215</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -8597,7 +8597,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>138.9257839476051</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -8670,13 +8670,13 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>220.0898510449805</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>230.3462332272727</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -8685,7 +8685,7 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>231.2329957552695</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -8749,10 +8749,10 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>137.841438974359</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>138.5543797798742</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -8761,7 +8761,7 @@
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>142.5962444444444</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
@@ -8837,7 +8837,7 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>127.6855444652332</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -8907,22 +8907,22 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>220.0898510449805</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>235.7664149699872</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>229.4130635965909</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>230.0982114216867</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>231.2329957552695</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -8989,22 +8989,22 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>138.5543797798742</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>131.3417120833333</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>133.9744074143302</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>139.9817740860215</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -9144,22 +9144,22 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>220.0898510449805</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>230.3462332272727</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>229.4130635965909</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>231.2329957552695</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -9223,13 +9223,13 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>137.841438974359</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>138.5543797798742</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>142.1340339220183</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -9238,10 +9238,10 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>133.9744074143302</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>139.9817740860215</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -9308,13 +9308,13 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>138.9257839476051</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>138.4565384518428</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
@@ -9384,7 +9384,7 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>235.7664149699872</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -9393,7 +9393,7 @@
         <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>230.0982114216867</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
@@ -9463,13 +9463,13 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>138.5543797798742</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>142.1340339220183</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>131.3417120833333</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -9478,7 +9478,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>139.9817740860215</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -9548,10 +9548,10 @@
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>127.6855444652332</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>138.4565384518428</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
         <v>0</v>
@@ -9618,16 +9618,16 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>220.0898510449805</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>235.7664149699872</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>229.4130635965909</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -9700,22 +9700,22 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>138.5543797798742</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>142.1340339220183</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>142.5962444444444</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>133.9744074143302</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>139.9817740860215</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -9779,7 +9779,7 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>134.8846762812383</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
@@ -9788,7 +9788,7 @@
         <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>138.4565384518428</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
         <v>0</v>
@@ -9855,22 +9855,22 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>220.0898510449805</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>230.3462332272727</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>229.4130635965909</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>230.0982114216867</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>231.2329957552695</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -9934,10 +9934,10 @@
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>137.841438974359</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>138.5543797798742</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
@@ -9952,7 +9952,7 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>139.9817740860215</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -10016,13 +10016,13 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>134.8846762812383</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>127.6855444652332</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -10092,22 +10092,22 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>220.0898510449805</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>230.3462332272727</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>230.0982114216867</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>231.2329957552695</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -10171,19 +10171,19 @@
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>137.841438974359</v>
+        <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>138.5543797798742</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>142.1340339220183</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
         <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>142.5962444444444</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
         <v>0</v>
@@ -10253,13 +10253,13 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>134.8846762812383</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>127.6855444652332</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -10329,10 +10329,10 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>220.0898510449805</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>235.7664149699872</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -10341,10 +10341,10 @@
         <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>230.0982114216867</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>231.2329957552695</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -10420,13 +10420,13 @@
         <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>142.5962444444444</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>133.9744074143302</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>139.9817740860215</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -10493,7 +10493,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>138.9257839476051</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
         <v>0</v>
@@ -10566,13 +10566,13 @@
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>220.0898510449805</v>
+        <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>235.7664149699872</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>230.3462332272727</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
@@ -10645,10 +10645,10 @@
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>137.841438974359</v>
+        <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>138.5543797798742</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
@@ -10660,7 +10660,7 @@
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>133.9744074143302</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -10727,10 +10727,10 @@
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>134.8846762812383</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>138.9257839476051</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
         <v>0</v>
@@ -10806,10 +10806,10 @@
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>235.7664149699872</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>230.3462332272727</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
         <v>0</v>
@@ -10885,22 +10885,22 @@
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>138.5543797798742</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>142.1340339220183</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>131.3417120833333</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>133.9744074143302</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>139.9817740860215</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
@@ -10973,7 +10973,7 @@
         <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>138.4565384518428</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
         <v>0</v>
@@ -11043,16 +11043,16 @@
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>235.7664149699872</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>230.3462332272727</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
         <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>230.0982114216867</v>
+        <v>0</v>
       </c>
       <c r="P41" t="n">
         <v>0</v>
@@ -11122,16 +11122,16 @@
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>138.5543797798742</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>131.3417120833333</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>142.5962444444444</v>
+        <v>0</v>
       </c>
       <c r="P42" t="n">
         <v>0</v>
@@ -11201,16 +11201,16 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>134.8846762812383</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>127.6855444652332</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>138.4565384518428</v>
+        <v>0</v>
       </c>
       <c r="P43" t="n">
         <v>0</v>
@@ -11280,13 +11280,13 @@
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>235.7664149699872</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>230.3462332272727</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>229.4130635965909</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -11359,10 +11359,10 @@
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>138.5543797798742</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>142.1340339220183</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
         <v>0</v>
@@ -11374,7 +11374,7 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>139.9817740860215</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
         <v>0</v>
@@ -11438,10 +11438,10 @@
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>134.8846762812383</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>138.9257839476051</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
         <v>0</v>
@@ -22534,7 +22534,7 @@
         <v>220.0898510449805</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>235.7664149699872</v>
       </c>
       <c r="M2" t="n">
         <v>230.3462332272727</v>
@@ -22543,7 +22543,7 @@
         <v>229.4130635965909</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>230.0982114216867</v>
       </c>
       <c r="P2" t="n">
         <v>231.2329957552695</v>
@@ -22616,16 +22616,16 @@
         <v>138.5543797798742</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q3" t="n">
         <v>139.9817740860215</v>
@@ -22692,16 +22692,16 @@
         <v>129.0132581705354</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>134.8846762812383</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>138.9257839476051</v>
       </c>
       <c r="N4" t="n">
         <v>127.6855444652332</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>138.4565384518428</v>
       </c>
       <c r="P4" t="n">
         <v>137.7280040491476</v>
@@ -22771,19 +22771,19 @@
         <v>220.0898510449805</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>235.7664149699872</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>230.3462332272727</v>
       </c>
       <c r="N5" t="n">
         <v>229.4130635965909</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>230.0982114216867</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>231.2329957552695</v>
       </c>
       <c r="Q5" t="n">
         <v>222.3056898744495</v>
@@ -22850,7 +22850,7 @@
         <v>137.841438974359</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M6" t="n">
         <v>142.1340339220183</v>
@@ -22859,13 +22859,13 @@
         <v>131.3417120833333</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R6" t="n">
         <v>145.679503963964</v>
@@ -22929,10 +22929,10 @@
         <v>129.0132581705354</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>134.8846762812383</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>138.9257839476051</v>
       </c>
       <c r="N7" t="n">
         <v>127.6855444652332</v>
@@ -23005,7 +23005,7 @@
         <v>181.0459045266863</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>220.0898510449805</v>
       </c>
       <c r="L8" t="n">
         <v>235.7664149699872</v>
@@ -23017,10 +23017,10 @@
         <v>229.4130635965909</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>230.0982114216867</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>231.2329957552695</v>
       </c>
       <c r="Q8" t="n">
         <v>222.3056898744495</v>
@@ -23087,7 +23087,7 @@
         <v>137.841438974359</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M9" t="n">
         <v>142.1340339220183</v>
@@ -23096,13 +23096,13 @@
         <v>131.3417120833333</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R9" t="n">
         <v>145.679503963964</v>
@@ -23169,7 +23169,7 @@
         <v>134.8846762812383</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>138.9257839476051</v>
       </c>
       <c r="N10" t="n">
         <v>127.6855444652332</v>
@@ -23242,13 +23242,13 @@
         <v>181.0459045266863</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>220.0898510449805</v>
       </c>
       <c r="L11" t="n">
         <v>235.7664149699872</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>230.3462332272727</v>
       </c>
       <c r="N11" t="n">
         <v>229.4130635965909</v>
@@ -23257,7 +23257,7 @@
         <v>230.0982114216867</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>231.2329957552695</v>
       </c>
       <c r="Q11" t="n">
         <v>222.3056898744495</v>
@@ -23321,10 +23321,10 @@
         <v>126.8376266666667</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M12" t="n">
         <v>142.1340339220183</v>
@@ -23333,7 +23333,7 @@
         <v>131.3417120833333</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P12" t="n">
         <v>133.9744074143302</v>
@@ -23409,7 +23409,7 @@
         <v>138.9257839476051</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>127.6855444652332</v>
       </c>
       <c r="O13" t="n">
         <v>138.4565384518428</v>
@@ -23479,22 +23479,22 @@
         <v>181.0459045266863</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>220.0898510449805</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>235.7664149699872</v>
       </c>
       <c r="M14" t="n">
         <v>230.3462332272727</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>229.4130635965909</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>230.0982114216867</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>231.2329957552695</v>
       </c>
       <c r="Q14" t="n">
         <v>222.3056898744495</v>
@@ -23561,22 +23561,22 @@
         <v>137.841438974359</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M15" t="n">
         <v>142.1340339220183</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O15" t="n">
         <v>142.5962444444444</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R15" t="n">
         <v>145.679503963964</v>
@@ -23716,22 +23716,22 @@
         <v>181.0459045266863</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>220.0898510449805</v>
       </c>
       <c r="L17" t="n">
         <v>235.7664149699872</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>230.3462332272727</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>229.4130635965909</v>
       </c>
       <c r="O17" t="n">
         <v>230.0982114216867</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>231.2329957552695</v>
       </c>
       <c r="Q17" t="n">
         <v>222.3056898744495</v>
@@ -23795,13 +23795,13 @@
         <v>126.8376266666667</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N18" t="n">
         <v>131.3417120833333</v>
@@ -23810,10 +23810,10 @@
         <v>142.5962444444444</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R18" t="n">
         <v>145.679503963964</v>
@@ -23880,13 +23880,13 @@
         <v>134.8846762812383</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>138.9257839476051</v>
       </c>
       <c r="N19" t="n">
         <v>127.6855444652332</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>138.4565384518428</v>
       </c>
       <c r="P19" t="n">
         <v>137.7280040491476</v>
@@ -23956,7 +23956,7 @@
         <v>220.0898510449805</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>235.7664149699872</v>
       </c>
       <c r="M20" t="n">
         <v>230.3462332272727</v>
@@ -23965,7 +23965,7 @@
         <v>229.4130635965909</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>230.0982114216867</v>
       </c>
       <c r="P20" t="n">
         <v>231.2329957552695</v>
@@ -24035,13 +24035,13 @@
         <v>137.841438974359</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O21" t="n">
         <v>142.5962444444444</v>
@@ -24050,7 +24050,7 @@
         <v>133.9744074143302</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R21" t="n">
         <v>145.679503963964</v>
@@ -24120,10 +24120,10 @@
         <v>138.9257839476051</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>127.6855444652332</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>138.4565384518428</v>
       </c>
       <c r="P22" t="n">
         <v>137.7280040491476</v>
@@ -24190,16 +24190,16 @@
         <v>181.0459045266863</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>220.0898510449805</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>235.7664149699872</v>
       </c>
       <c r="M23" t="n">
         <v>230.3462332272727</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>229.4130635965909</v>
       </c>
       <c r="O23" t="n">
         <v>230.0982114216867</v>
@@ -24272,22 +24272,22 @@
         <v>137.841438974359</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N24" t="n">
         <v>131.3417120833333</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R24" t="n">
         <v>145.679503963964</v>
@@ -24351,7 +24351,7 @@
         <v>129.0132581705354</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>134.8846762812383</v>
       </c>
       <c r="M25" t="n">
         <v>138.9257839476051</v>
@@ -24360,7 +24360,7 @@
         <v>127.6855444652332</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>138.4565384518428</v>
       </c>
       <c r="P25" t="n">
         <v>137.7280040491476</v>
@@ -24427,22 +24427,22 @@
         <v>181.0459045266863</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>220.0898510449805</v>
       </c>
       <c r="L26" t="n">
         <v>235.7664149699872</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>230.3462332272727</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>229.4130635965909</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>230.0982114216867</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>231.2329957552695</v>
       </c>
       <c r="Q26" t="n">
         <v>222.3056898744495</v>
@@ -24506,10 +24506,10 @@
         <v>126.8376266666667</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M27" t="n">
         <v>142.1340339220183</v>
@@ -24524,7 +24524,7 @@
         <v>133.9744074143302</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R27" t="n">
         <v>145.679503963964</v>
@@ -24588,13 +24588,13 @@
         <v>129.0132581705354</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>134.8846762812383</v>
       </c>
       <c r="M28" t="n">
         <v>138.9257839476051</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>127.6855444652332</v>
       </c>
       <c r="O28" t="n">
         <v>138.4565384518428</v>
@@ -24664,22 +24664,22 @@
         <v>181.0459045266863</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>220.0898510449805</v>
       </c>
       <c r="L29" t="n">
         <v>235.7664149699872</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>230.3462332272727</v>
       </c>
       <c r="N29" t="n">
         <v>229.4130635965909</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>230.0982114216867</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>231.2329957552695</v>
       </c>
       <c r="Q29" t="n">
         <v>222.3056898744495</v>
@@ -24743,19 +24743,19 @@
         <v>126.8376266666667</v>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N30" t="n">
         <v>131.3417120833333</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P30" t="n">
         <v>133.9744074143302</v>
@@ -24825,13 +24825,13 @@
         <v>129.0132581705354</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>134.8846762812383</v>
       </c>
       <c r="M31" t="n">
         <v>138.9257839476051</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>127.6855444652332</v>
       </c>
       <c r="O31" t="n">
         <v>138.4565384518428</v>
@@ -24901,10 +24901,10 @@
         <v>181.0459045266863</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>220.0898510449805</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>235.7664149699872</v>
       </c>
       <c r="M32" t="n">
         <v>230.3462332272727</v>
@@ -24913,10 +24913,10 @@
         <v>229.4130635965909</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>230.0982114216867</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>231.2329957552695</v>
       </c>
       <c r="Q32" t="n">
         <v>222.3056898744495</v>
@@ -24992,13 +24992,13 @@
         <v>131.3417120833333</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R33" t="n">
         <v>145.679503963964</v>
@@ -25065,7 +25065,7 @@
         <v>134.8846762812383</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>138.9257839476051</v>
       </c>
       <c r="N34" t="n">
         <v>127.6855444652332</v>
@@ -25138,13 +25138,13 @@
         <v>181.0459045266863</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>220.0898510449805</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>235.7664149699872</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>230.3462332272727</v>
       </c>
       <c r="N35" t="n">
         <v>229.4130635965909</v>
@@ -25217,10 +25217,10 @@
         <v>126.8376266666667</v>
       </c>
       <c r="K36" t="n">
-        <v>0</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M36" t="n">
         <v>142.1340339220183</v>
@@ -25232,7 +25232,7 @@
         <v>142.5962444444444</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q36" t="n">
         <v>139.9817740860215</v>
@@ -25299,10 +25299,10 @@
         <v>129.0132581705354</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>134.8846762812383</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>138.9257839476051</v>
       </c>
       <c r="N37" t="n">
         <v>127.6855444652332</v>
@@ -25378,10 +25378,10 @@
         <v>220.0898510449805</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>235.7664149699872</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>230.3462332272727</v>
       </c>
       <c r="N38" t="n">
         <v>229.4130635965909</v>
@@ -25457,22 +25457,22 @@
         <v>137.841438974359</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O39" t="n">
         <v>142.5962444444444</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R39" t="n">
         <v>145.679503963964</v>
@@ -25545,7 +25545,7 @@
         <v>127.6855444652332</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>138.4565384518428</v>
       </c>
       <c r="P40" t="n">
         <v>137.7280040491476</v>
@@ -25615,16 +25615,16 @@
         <v>220.0898510449805</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>235.7664149699872</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>230.3462332272727</v>
       </c>
       <c r="N41" t="n">
         <v>229.4130635965909</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>230.0982114216867</v>
       </c>
       <c r="P41" t="n">
         <v>231.2329957552695</v>
@@ -25694,16 +25694,16 @@
         <v>137.841438974359</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M42" t="n">
         <v>142.1340339220183</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P42" t="n">
         <v>133.9744074143302</v>
@@ -25773,16 +25773,16 @@
         <v>129.0132581705354</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>134.8846762812383</v>
       </c>
       <c r="M43" t="n">
         <v>138.9257839476051</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>127.6855444652332</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>138.4565384518428</v>
       </c>
       <c r="P43" t="n">
         <v>137.7280040491476</v>
@@ -25852,13 +25852,13 @@
         <v>220.0898510449805</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>235.7664149699872</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>230.3462332272727</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>229.4130635965909</v>
       </c>
       <c r="O44" t="n">
         <v>230.0982114216867</v>
@@ -25931,10 +25931,10 @@
         <v>137.841438974359</v>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N45" t="n">
         <v>131.3417120833333</v>
@@ -25946,7 +25946,7 @@
         <v>133.9744074143302</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R45" t="n">
         <v>145.679503963964</v>
@@ -26010,10 +26010,10 @@
         <v>129.0132581705354</v>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>134.8846762812383</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>138.9257839476051</v>
       </c>
       <c r="N46" t="n">
         <v>127.6855444652332</v>
@@ -26078,7 +26078,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>123023.5991224671</v>
+        <v>-1.209627953357994e-11</v>
       </c>
     </row>
     <row r="3">
@@ -26086,7 +26086,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>181881.8933680103</v>
+        <v>-1.209627953357994e-11</v>
       </c>
     </row>
     <row r="4">
@@ -26094,7 +26094,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>141945.7613208857</v>
+        <v>-1.209627953357994e-11</v>
       </c>
     </row>
     <row r="5">
@@ -26102,7 +26102,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>131408.5068047156</v>
+        <v>-1.209627953357994e-11</v>
       </c>
     </row>
     <row r="6">
@@ -26110,7 +26110,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>200075.2934582162</v>
+        <v>-1.209627953357994e-11</v>
       </c>
     </row>
     <row r="7">
@@ -26118,7 +26118,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>189946.2638835197</v>
+        <v>-1.209627953357994e-11</v>
       </c>
     </row>
     <row r="8">
@@ -26126,7 +26126,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>117032.1929093238</v>
+        <v>-1.209627953357994e-11</v>
       </c>
     </row>
     <row r="9">
@@ -26134,7 +26134,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>158673.6189354638</v>
+        <v>-1.209627953357994e-11</v>
       </c>
     </row>
     <row r="10">
@@ -26142,7 +26142,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>200889.5901179787</v>
+        <v>-1.209627953357994e-11</v>
       </c>
     </row>
     <row r="11">
@@ -26150,7 +26150,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>179672.6893765823</v>
+        <v>-1.209627953357994e-11</v>
       </c>
     </row>
     <row r="12">
@@ -26158,7 +26158,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>164507.2879465382</v>
+        <v>-1.209627953357994e-11</v>
       </c>
     </row>
     <row r="13">
@@ -26166,7 +26166,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>137537.518255763</v>
+        <v>-1.209627953357994e-11</v>
       </c>
     </row>
     <row r="14">
@@ -26174,7 +26174,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>121644.8505094455</v>
+        <v>-1.209627953357994e-11</v>
       </c>
     </row>
     <row r="15">
@@ -26182,7 +26182,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>144432.2279852762</v>
+        <v>-1.209627953357994e-11</v>
       </c>
     </row>
     <row r="16">
@@ -26190,7 +26190,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>139600.4989163581</v>
+        <v>-1.209627953357994e-11</v>
       </c>
     </row>
   </sheetData>
